--- a/MU/Test upload format/SHG/2028 - 2029 - SHG/Q1 28-29 - SHG.xlsx
+++ b/MU/Test upload format/SHG/2028 - 2029 - SHG/Q1 28-29 - SHG.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AK$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AO$18</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="115">
   <si>
     <t>loancat</t>
   </si>
@@ -375,9 +375,6 @@
   </si>
   <si>
     <t>Q1282917</t>
-  </si>
-  <si>
-    <t>300000</t>
   </si>
 </sst>
 </file>
@@ -775,27 +772,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -920,7 +902,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -932,34 +914,34 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1059,7 +1041,7 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -1077,7 +1059,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -1085,7 +1067,7 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -3116,7 +3098,7 @@
       <c r="Q15" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="R15" s="21" t="s">
+      <c r="R15" s="14" t="s">
         <v>106</v>
       </c>
       <c r="S15" s="16" t="s">
@@ -3226,8 +3208,8 @@
       <c r="Q16" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="R16" s="21" t="s">
-        <v>45</v>
+      <c r="R16" s="14" t="s">
+        <v>97</v>
       </c>
       <c r="S16" s="16" t="s">
         <v>50</v>
@@ -3452,8 +3434,8 @@
       <c r="Q18" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="R18" s="25" t="s">
-        <v>115</v>
+      <c r="R18" s="14" t="s">
+        <v>97</v>
       </c>
       <c r="S18" s="23" t="s">
         <v>50</v>
@@ -3514,7 +3496,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AK18" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AO18" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
